--- a/实验设计/符号表管理/符号表格/符号表管理表.xlsx
+++ b/实验设计/符号表管理/符号表格/符号表管理表.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:255</t>
+          <t>include/minic/interface.hpp:250</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:256</t>
+          <t>include/minic/interface.hpp:251</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:257</t>
+          <t>include/minic/interface.hpp:252</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:258</t>
+          <t>include/minic/interface.hpp:253</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:259</t>
+          <t>include/minic/interface.hpp:254</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:260</t>
+          <t>include/minic/interface.hpp:255</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:261</t>
+          <t>include/minic/interface.hpp:256</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:262</t>
+          <t>include/minic/interface.hpp:257</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:263</t>
+          <t>include/minic/interface.hpp:258</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:264</t>
+          <t>include/minic/interface.hpp:259</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:265</t>
+          <t>include/minic/interface.hpp:260</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:270</t>
+          <t>include/minic/interface.hpp:265</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:271</t>
+          <t>include/minic/interface.hpp:266</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:272</t>
+          <t>include/minic/interface.hpp:267</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:273</t>
+          <t>include/minic/interface.hpp:268</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:281</t>
+          <t>include/minic/interface.hpp:276</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:282</t>
+          <t>include/minic/interface.hpp:277</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:283</t>
+          <t>include/minic/interface.hpp:278</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:284</t>
+          <t>include/minic/interface.hpp:279</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:285</t>
+          <t>include/minic/interface.hpp:280</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:286</t>
+          <t>include/minic/interface.hpp:281</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:287</t>
+          <t>include/minic/interface.hpp:282</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:288</t>
+          <t>include/minic/interface.hpp:283</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:289</t>
+          <t>include/minic/interface.hpp:284</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:297</t>
+          <t>include/minic/interface.hpp:292</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:298</t>
+          <t>include/minic/interface.hpp:293</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:299</t>
+          <t>include/minic/interface.hpp:294</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:300</t>
+          <t>include/minic/interface.hpp:295</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:301</t>
+          <t>include/minic/interface.hpp:296</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:302</t>
+          <t>include/minic/interface.hpp:297</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:307</t>
+          <t>include/minic/interface.hpp:302</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:308</t>
+          <t>include/minic/interface.hpp:303</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:309</t>
+          <t>include/minic/interface.hpp:304</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:310</t>
+          <t>include/minic/interface.hpp:305</t>
         </is>
       </c>
     </row>
